--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מאיר בן הרוש - צל עץ תמר קאבר</v>
+        <v>צורי תלבי - אמא קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409769&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409775&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-26</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מאיר בן הרוש - צל עץ תמר קאבר</v>
+        <v>צורי תלבי - אמא קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>לינוי אוחנה - שכחת את הכל קאבר</v>
+        <v>חנוך שובל - פיסה מזכרוני קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409768&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409774&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-26</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>לינוי אוחנה - שכחת את הכל קאבר</v>
+        <v>חנוך שובל - פיסה מזכרוני קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאם פרץ - צעקתי בלילה קאבר</v>
+        <v>נתנאל ביטון - פינה של שקט קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409767&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409773&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-26</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאם פרץ - צעקתי בלילה קאבר</v>
+        <v>נתנאל ביטון - פינה של שקט קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ליאור קקון - היום קמתי שמח קאבר</v>
+        <v>משה כהן - שלווה בארמונותייך &amp; תפילות קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409766&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409772&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-26</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ליאור קקון - היום קמתי שמח קאבר</v>
+        <v>משה כהן - שלווה בארמונותייך &amp; תפילות קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליאור לוי - אלוהים אלוהים קאבר</v>
+        <v>גלית - מאשאפ חתונה 2026</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409765&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409771&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-26</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליאור לוי - אלוהים אלוהים קאבר</v>
+        <v>גלית - מאשאפ חתונה 2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ליאור חייט - יש בך הכל קאבר</v>
+        <v>גלית - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409764&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409770&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-26</v>
@@ -659,392 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ליאור חייט - יש בך הכל קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>יהונתן לוי - אם אשכחך קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409763&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>יהונתן לוי - אם אשכחך קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>חן גז - רולקס וקסקט קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409762&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>חן גז - רולקס וקסקט קאבר</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>חיים משה - בואי בשלום קאבר</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409761&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>חיים משה - בואי בשלום קאבר</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>הראל מעודה - תמיד שמח קאבר</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409760&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>הראל מעודה - תמיד שמח קאבר</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>בן מירן - רק אל תגידי קאבר</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409759&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>בן מירן - רק אל תגידי קאבר</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>בן יוסף דניאל - אני מקווה קאבר</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409758&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>בן יוסף דניאל - אני מקווה קאבר</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אריאל דימנט - כשאתה קאבר</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409757&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אריאל דימנט - כשאתה קאבר</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אלון דהן - נבראתי לך קאבר</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409756&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אלון דהן - נבראתי לך קאבר</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>אלון דהן - דברים שרציתי לומר קאבר</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409755&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>אלון דהן - דברים שרציתי לומר קאבר</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>איתמר הרוש - ממעמקים &amp; תפילות</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409754&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v>איתמר הרוש - ממעמקים &amp; תפילות</v>
+        <v>גלית - לאהוב אותך כל יום קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צורי תלבי - אמא קאבר</v>
+        <v>שיר מזרחי - ממעמקים &amp; הנך יפה קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409775&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409782&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-26</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צורי תלבי - אמא קאבר</v>
+        <v>שיר מזרחי - ממעמקים &amp; הנך יפה קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>חנוך שובל - פיסה מזכרוני קאבר</v>
+        <v>שיר חסון - עכשיו התור לאהבה קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409774&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409781&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-26</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>חנוך שובל - פיסה מזכרוני קאבר</v>
+        <v>שיר חסון - עכשיו התור לאהבה קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נתנאל ביטון - פינה של שקט קאבר</v>
+        <v>שילת סופר - מרצדס שחורה קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409773&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409780&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-26</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נתנאל ביטון - פינה של שקט קאבר</v>
+        <v>שילת סופר - מרצדס שחורה קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>משה כהן - שלווה בארמונותייך &amp; תפילות קאבר</v>
+        <v>שגיא גטר - הסכם שלום (צרפתית) + מדאם</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409772&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409779&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-26</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>משה כהן - שלווה בארמונותייך &amp; תפילות קאבר</v>
+        <v>שגיא גטר - הסכם שלום (צרפתית) + מדאם</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>גלית - מאשאפ חתונה 2026</v>
+        <v>קורין גמליאל - סינדרלה קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409771&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409778&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-26</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>גלית - מאשאפ חתונה 2026</v>
+        <v>קורין גמליאל - סינדרלה קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>גלית - לאהוב אותך כל יום קאבר</v>
+        <v>צורי תלבי - איפה את קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409770&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409777&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-26</v>
@@ -659,12 +659,50 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>גלית - לאהוב אותך כל יום קאבר</v>
+        <v>צורי תלבי - איפה את קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>מיקו אנג'ל &amp; ישראל שטרית - אמא אל תבכי קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409776&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>מיקו אנג'ל &amp; ישראל שטרית - אמא אל תבכי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>